--- a/data/sars/pacific/tables/Pacific_2016_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2016_Appendix3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C1B6A2-FFED-CC4C-BF61-814F4F4B5FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39429D3D-FFE0-624E-9D8F-1D3C9A8F9A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="28520" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="129">
   <si>
     <t>California sea lion (U.S.)</t>
   </si>
@@ -388,13 +388,25 @@
     <t>survey2</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>False killer whale (Main Hawaiian Islands Insular)</t>
   </si>
   <si>
     <t>rf</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>RF=0.2 in SAR; RF=0.1 was typo in table</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -405,7 +417,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -422,6 +434,12 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -449,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -506,6 +524,9 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -811,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="72.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -825,13 +846,14 @@
     <col min="9" max="9" width="14.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="45.796875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="23.19921875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="14" max="14" width="12.59765625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.796875" style="1" customWidth="1"/>
+    <col min="16" max="17" width="45.796875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="23.19921875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>110</v>
       </c>
@@ -848,7 +870,7 @@
         <v>114</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>115</v>
@@ -872,10 +894,16 @@
         <v>120</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+        <v>126</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -918,8 +946,9 @@
       <c r="N2" s="10">
         <v>2014</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -962,8 +991,9 @@
       <c r="N3" s="10">
         <v>2014</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -1002,8 +1032,9 @@
       <c r="N4" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1042,8 +1073,9 @@
       <c r="N5" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -1082,8 +1114,9 @@
       <c r="N6" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1122,8 +1155,9 @@
       <c r="N7" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -1166,8 +1200,9 @@
       <c r="N8" s="10">
         <v>2014</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -1210,8 +1245,11 @@
       <c r="N9" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O9" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -1254,8 +1292,9 @@
       <c r="N10" s="10">
         <v>2015</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O10" s="10"/>
+    </row>
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
@@ -1298,8 +1337,11 @@
       <c r="N11" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O11" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
@@ -1342,8 +1384,9 @@
       <c r="N12" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O12" s="10"/>
+    </row>
+    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -1386,8 +1429,9 @@
       <c r="N13" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -1430,8 +1474,9 @@
       <c r="N14" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O14" s="10"/>
+    </row>
+    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -1474,8 +1519,9 @@
       <c r="N15" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O15" s="10"/>
+    </row>
+    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -1518,8 +1564,9 @@
       <c r="N16" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O16" s="10"/>
+    </row>
+    <row r="17" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
         <v>26</v>
       </c>
@@ -1562,8 +1609,11 @@
       <c r="N17" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O17" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
         <v>28</v>
       </c>
@@ -1606,8 +1656,11 @@
       <c r="N18" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O18" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
@@ -1650,8 +1703,11 @@
       <c r="N19" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O19" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
@@ -1694,8 +1750,11 @@
       <c r="N20" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O20" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
         <v>32</v>
       </c>
@@ -1738,8 +1797,11 @@
       <c r="N21" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O21" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
         <v>35</v>
       </c>
@@ -1782,8 +1844,11 @@
       <c r="N22" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O22" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
@@ -1826,8 +1891,11 @@
       <c r="N23" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O23" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
@@ -1870,8 +1938,11 @@
       <c r="N24" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O24" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
@@ -1914,8 +1985,11 @@
       <c r="N25" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O25" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
@@ -1958,8 +2032,11 @@
       <c r="N26" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O26" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
@@ -2002,8 +2079,9 @@
       <c r="N27" s="10">
         <v>2016</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O27" s="10"/>
+    </row>
+    <row r="28" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
         <v>44</v>
       </c>
@@ -2046,8 +2124,11 @@
       <c r="N28" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O28" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="5" t="s">
         <v>45</v>
       </c>
@@ -2090,8 +2171,11 @@
       <c r="N29" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O29" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>46</v>
       </c>
@@ -2134,8 +2218,9 @@
       <c r="N30" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O30" s="10"/>
+    </row>
+    <row r="31" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
         <v>47</v>
       </c>
@@ -2178,8 +2263,9 @@
       <c r="N31" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O31" s="10"/>
+    </row>
+    <row r="32" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
         <v>48</v>
       </c>
@@ -2222,8 +2308,9 @@
       <c r="N32" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O32" s="10"/>
+    </row>
+    <row r="33" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
         <v>49</v>
       </c>
@@ -2266,8 +2353,11 @@
       <c r="N33" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O33" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="5" t="s">
         <v>50</v>
       </c>
@@ -2310,9 +2400,12 @@
       <c r="N34" s="14">
         <v>2016</v>
       </c>
-      <c r="O34" s="2"/>
-    </row>
-    <row r="35" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O34" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="4" t="s">
         <v>51</v>
       </c>
@@ -2355,9 +2448,10 @@
       <c r="N35" s="10">
         <v>2014</v>
       </c>
-      <c r="O35" s="2"/>
-    </row>
-    <row r="36" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O35" s="10"/>
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="4" t="s">
         <v>52</v>
       </c>
@@ -2400,9 +2494,10 @@
       <c r="N36" s="10">
         <v>2014</v>
       </c>
-      <c r="O36" s="2"/>
-    </row>
-    <row r="37" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O36" s="10"/>
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
         <v>53</v>
       </c>
@@ -2441,9 +2536,10 @@
       <c r="N37" s="10">
         <v>2014</v>
       </c>
-      <c r="O37" s="2"/>
-    </row>
-    <row r="38" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O37" s="10"/>
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="5" t="s">
         <v>54</v>
       </c>
@@ -2486,9 +2582,12 @@
       <c r="N38" s="14">
         <v>2016</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O38" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
         <v>57</v>
       </c>
@@ -2531,9 +2630,10 @@
       <c r="N39" s="10">
         <v>2015</v>
       </c>
-      <c r="O39" s="2"/>
-    </row>
-    <row r="40" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O39" s="10"/>
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="5" t="s">
         <v>58</v>
       </c>
@@ -2576,8 +2676,11 @@
       <c r="N40" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O40" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="s">
         <v>61</v>
       </c>
@@ -2620,8 +2723,11 @@
       <c r="N41" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O41" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="5" t="s">
         <v>62</v>
       </c>
@@ -2664,8 +2770,11 @@
       <c r="N42" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O42" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
         <v>64</v>
       </c>
@@ -2708,8 +2817,9 @@
       <c r="N43" s="10">
         <v>2015</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O43" s="10"/>
+    </row>
+    <row r="44" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="s">
         <v>65</v>
       </c>
@@ -2750,8 +2860,9 @@
       <c r="N44" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O44" s="10"/>
+    </row>
+    <row r="45" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="4" t="s">
         <v>66</v>
       </c>
@@ -2794,8 +2905,9 @@
       <c r="N45" s="10">
         <v>2010</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O45" s="10"/>
+    </row>
+    <row r="46" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="4" t="s">
         <v>67</v>
       </c>
@@ -2836,8 +2948,9 @@
       <c r="N46" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O46" s="10"/>
+    </row>
+    <row r="47" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="4" t="s">
         <v>68</v>
       </c>
@@ -2878,8 +2991,9 @@
       <c r="N47" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="O47" s="10"/>
+    </row>
+    <row r="48" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="4" t="s">
         <v>69</v>
       </c>
@@ -2922,8 +3036,9 @@
       <c r="N48" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O48" s="10"/>
+    </row>
+    <row r="49" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="4" t="s">
         <v>70</v>
       </c>
@@ -2966,8 +3081,9 @@
       <c r="N49" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O49" s="10"/>
+    </row>
+    <row r="50" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="4" t="s">
         <v>71</v>
       </c>
@@ -3010,8 +3126,9 @@
       <c r="N50" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O50" s="10"/>
+    </row>
+    <row r="51" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="s">
         <v>72</v>
       </c>
@@ -3054,8 +3171,9 @@
       <c r="N51" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O51" s="10"/>
+    </row>
+    <row r="52" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="4" t="s">
         <v>73</v>
       </c>
@@ -3096,8 +3214,9 @@
       <c r="N52" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O52" s="10"/>
+    </row>
+    <row r="53" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="4" t="s">
         <v>74</v>
       </c>
@@ -3136,8 +3255,9 @@
       <c r="N53" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O53" s="10"/>
+    </row>
+    <row r="54" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="4" t="s">
         <v>75</v>
       </c>
@@ -3176,8 +3296,9 @@
       <c r="N54" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O54" s="10"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="4" t="s">
         <v>76</v>
       </c>
@@ -3216,8 +3337,9 @@
       <c r="N55" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O55" s="10"/>
+    </row>
+    <row r="56" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="4" t="s">
         <v>77</v>
       </c>
@@ -3258,8 +3380,9 @@
       <c r="N56" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O56" s="10"/>
+    </row>
+    <row r="57" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="4" t="s">
         <v>78</v>
       </c>
@@ -3302,8 +3425,9 @@
       <c r="N57" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O57" s="10"/>
+    </row>
+    <row r="58" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="4" t="s">
         <v>79</v>
       </c>
@@ -3346,8 +3470,9 @@
       <c r="N58" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O58" s="10"/>
+    </row>
+    <row r="59" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="4" t="s">
         <v>80</v>
       </c>
@@ -3390,8 +3515,9 @@
       <c r="N59" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O59" s="10"/>
+    </row>
+    <row r="60" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="4" t="s">
         <v>81</v>
       </c>
@@ -3432,8 +3558,9 @@
       <c r="N60" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O60" s="10"/>
+    </row>
+    <row r="61" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="4" t="s">
         <v>82</v>
       </c>
@@ -3472,8 +3599,9 @@
       <c r="N61" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O61" s="10"/>
+    </row>
+    <row r="62" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="4" t="s">
         <v>83</v>
       </c>
@@ -3512,8 +3640,9 @@
       <c r="N62" s="10">
         <v>2010</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O62" s="10"/>
+    </row>
+    <row r="63" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="4" t="s">
         <v>84</v>
       </c>
@@ -3554,8 +3683,9 @@
       <c r="N63" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O63" s="10"/>
+    </row>
+    <row r="64" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="4" t="s">
         <v>85</v>
       </c>
@@ -3596,8 +3726,9 @@
       <c r="N64" s="10">
         <v>2010</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O64" s="10"/>
+    </row>
+    <row r="65" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="4" t="s">
         <v>86</v>
       </c>
@@ -3638,8 +3769,9 @@
       <c r="N65" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O65" s="10"/>
+    </row>
+    <row r="66" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="4" t="s">
         <v>87</v>
       </c>
@@ -3678,8 +3810,9 @@
       <c r="N66" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O66" s="10"/>
+    </row>
+    <row r="67" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="4" t="s">
         <v>88</v>
       </c>
@@ -3720,8 +3853,9 @@
       <c r="N67" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O67" s="10"/>
+    </row>
+    <row r="68" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="5" t="s">
         <v>89</v>
       </c>
@@ -3760,8 +3894,11 @@
       <c r="N68" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O68" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="5" t="s">
         <v>90</v>
       </c>
@@ -3802,8 +3939,11 @@
       <c r="N69" s="14">
         <v>2016</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O69" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="4" t="s">
         <v>91</v>
       </c>
@@ -3842,10 +3982,11 @@
       <c r="N70" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O70" s="10"/>
+    </row>
+    <row r="71" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B71" s="5">
         <v>151</v>
@@ -3886,8 +4027,11 @@
       <c r="N71" s="5">
         <v>2016</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O71" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="4" t="s">
         <v>92</v>
       </c>
@@ -3930,8 +4074,9 @@
       <c r="N72" s="10">
         <v>2010</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O72" s="10"/>
+    </row>
+    <row r="73" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="4" t="s">
         <v>93</v>
       </c>
@@ -3972,8 +4117,9 @@
       <c r="N73" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O73" s="10"/>
+    </row>
+    <row r="74" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="4" t="s">
         <v>94</v>
       </c>
@@ -4014,8 +4160,9 @@
       <c r="N74" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O74" s="10"/>
+    </row>
+    <row r="75" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="4" t="s">
         <v>95</v>
       </c>
@@ -4056,8 +4203,9 @@
       <c r="N75" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O75" s="10"/>
+    </row>
+    <row r="76" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="4" t="s">
         <v>96</v>
       </c>
@@ -4098,8 +4246,9 @@
       <c r="N76" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O76" s="10"/>
+    </row>
+    <row r="77" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="4" t="s">
         <v>97</v>
       </c>
@@ -4138,8 +4287,9 @@
       <c r="N77" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O77" s="10"/>
+    </row>
+    <row r="78" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A78" s="4" t="s">
         <v>98</v>
       </c>
@@ -4180,8 +4330,9 @@
       <c r="N78" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O78" s="10"/>
+    </row>
+    <row r="79" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="4" t="s">
         <v>99</v>
       </c>
@@ -4222,8 +4373,9 @@
       <c r="N79" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O79" s="10"/>
+    </row>
+    <row r="80" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="4" t="s">
         <v>100</v>
       </c>
@@ -4240,7 +4392,7 @@
         <v>0.04</v>
       </c>
       <c r="F80" s="11">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G80" s="11">
         <v>10.199999999999999</v>
@@ -4264,8 +4416,12 @@
       <c r="N80" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O80" s="10"/>
+      <c r="P80" s="19" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A81" s="4" t="s">
         <v>101</v>
       </c>
@@ -4306,8 +4462,9 @@
       <c r="N81" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O81" s="10"/>
+    </row>
+    <row r="82" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="4" t="s">
         <v>102</v>
       </c>
@@ -4348,8 +4505,9 @@
       <c r="N82" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O82" s="10"/>
+    </row>
+    <row r="83" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A83" s="4" t="s">
         <v>103</v>
       </c>
@@ -4390,8 +4548,9 @@
       <c r="N83" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O83" s="10"/>
+    </row>
+    <row r="84" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A84" s="4" t="s">
         <v>104</v>
       </c>
@@ -4432,8 +4591,9 @@
       <c r="N84" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O84" s="10"/>
+    </row>
+    <row r="85" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A85" s="4" t="s">
         <v>105</v>
       </c>
@@ -4474,8 +4634,9 @@
       <c r="N85" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O85" s="10"/>
+    </row>
+    <row r="86" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A86" s="4" t="s">
         <v>106</v>
       </c>
@@ -4518,8 +4679,9 @@
       <c r="N86" s="10">
         <v>2009</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O86" s="10"/>
+    </row>
+    <row r="87" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A87" s="4" t="s">
         <v>107</v>
       </c>
@@ -4562,8 +4724,9 @@
       <c r="N87" s="10">
         <v>2008</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O87" s="10"/>
+    </row>
+    <row r="88" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A88" s="4" t="s">
         <v>108</v>
       </c>
@@ -4606,6 +4769,7 @@
       <c r="N88" s="10">
         <v>2008</v>
       </c>
+      <c r="O88" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
